--- a/test_samples/CONG_THANH/sample2_ref.xlsx
+++ b/test_samples/CONG_THANH/sample2_ref.xlsx
@@ -1749,7 +1749,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Additional charge</t>
+          <t>10 kiện hàng bị ướt hư hết giày, Pousung khắc phục hậu quả tối đa còn phát sinh thệm 63.5USD (Tỷ giá: 26.241 ngày 15/1/2026). Công Thành trả phí phát sinh này (sử dụng invoice PSV0810666665 để cấn trừ)</t>
         </is>
       </c>
       <c r="F17" t="n">
